--- a/Tests/Validation/Wheat/data/FAR WAE W21-05.xlsx
+++ b/Tests/Validation/Wheat/data/FAR WAE W21-05.xlsx
@@ -1,32 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Observed" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observed" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,16 +48,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -417,121 +430,111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W91"/>
+  <dimension ref="A1:U91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>SimulationName</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Clock.Today</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Phenology.CurrentStageName</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Cultivar</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Potential</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>NDVIModel.Script.NDVI</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>NDVIModel.Script.NDVI.se</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt.se</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Population</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Population.se</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Population</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Population.se</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Spike.HeadNumber</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Spike.HeadNumber.se</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Density</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Density.se</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Wheat.Grain.Moisture</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Grain.WaterContent</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Moisture.se</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Protein</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Protein.se</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Screenings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Screenings.se</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt.se</t>
         </is>
@@ -543,30 +546,22 @@
           <t>FAR WAE W21-05CvTrojan</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="3" t="n">
         <v>44326</v>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
+      <c r="H2" t="n">
         <v>123.333333333333</v>
       </c>
-      <c r="K2" t="n">
+      <c r="I2" t="n">
         <v>1.11111111111111</v>
       </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -577,8 +572,6 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -586,26 +579,18 @@
           <t>FAR WAE W21-05CvTrojan</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="3" t="n">
         <v>44385</v>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+      <c r="D3" t="n">
         <v>0.5075</v>
       </c>
-      <c r="G3" t="n">
+      <c r="E3" t="n">
         <v>0.0165201896679992</v>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -620,8 +605,6 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -629,26 +612,18 @@
           <t>FAR WAE W21-05CvTrojan</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="3" t="n">
         <v>44397</v>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+      <c r="D4" t="n">
         <v>0.61</v>
       </c>
-      <c r="G4" t="n">
+      <c r="E4" t="n">
         <v>0.0339116499156264</v>
       </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -663,8 +638,6 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -672,26 +645,18 @@
           <t>FAR WAE W21-05CvTrojan</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="3" t="n">
         <v>44403</v>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
+      <c r="D5" t="n">
         <v>0.62</v>
       </c>
-      <c r="G5" t="n">
+      <c r="E5" t="n">
         <v>0.0324037034920393</v>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -706,8 +671,6 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -715,26 +678,18 @@
           <t>FAR WAE W21-05CvTrojan</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="3" t="n">
         <v>44484</v>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+      <c r="D6" t="n">
         <v>0.35</v>
       </c>
-      <c r="G6" t="n">
+      <c r="E6" t="n">
         <v>0.0168325082306035</v>
       </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -749,8 +704,6 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -758,26 +711,18 @@
           <t>FAR WAE W21-05CvTrojan</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="3" t="n">
         <v>44498</v>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="D7" t="n">
         <v>0.1825</v>
       </c>
-      <c r="G7" t="n">
+      <c r="E7" t="n">
         <v>0.0131497781983829</v>
       </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -792,8 +737,6 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -801,26 +744,18 @@
           <t>FAR WAE W21-05CvTrojan</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="3" t="n">
         <v>44502</v>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
+      <c r="D8" t="n">
         <v>0.1575</v>
       </c>
-      <c r="G8" t="n">
+      <c r="E8" t="n">
         <v>0.0047871355387817</v>
       </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -835,8 +770,6 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -844,7 +777,7 @@
           <t>FAR WAE W21-05CvTrojan</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -852,32 +785,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
         <v>1373.82726349707</v>
       </c>
-      <c r="I9" t="n">
+      <c r="G9" t="n">
         <v>0.931024115358576</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
         <v>363.549413896198</v>
       </c>
-      <c r="M9" t="n">
+      <c r="K9" t="n">
         <v>40.9162146108114</v>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -886,8 +811,6 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -895,7 +818,7 @@
           <t>FAR WAE W21-05CvTrojan</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="3" t="n">
         <v>44538</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -903,52 +826,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>78.7625</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.472219140512822</v>
+      </c>
       <c r="N10" t="n">
-        <v>78.7625</v>
+        <v>10.375</v>
       </c>
       <c r="O10" t="n">
-        <v>0.472219140512822</v>
+        <v>0.110867789130417</v>
       </c>
       <c r="P10" t="n">
-        <v>10.375</v>
+        <v>11.425</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.110867789130417</v>
+        <v>0.179698822107065</v>
       </c>
       <c r="R10" t="n">
-        <v>11.425</v>
+        <v>0.672321412397926</v>
       </c>
       <c r="S10" t="n">
-        <v>0.179698822107065</v>
+        <v>0.111913736451308</v>
       </c>
       <c r="T10" t="n">
-        <v>0.672321412397926</v>
+        <v>566.737304152969</v>
       </c>
       <c r="U10" t="n">
-        <v>0.111913736451308</v>
-      </c>
-      <c r="V10" t="n">
-        <v>566.737304152969</v>
-      </c>
-      <c r="W10" t="n">
         <v>0.155054268551307</v>
       </c>
     </row>
@@ -958,30 +871,22 @@
           <t>FAR WAE W21-05CvMagenta</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="3" t="n">
         <v>44326</v>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Magenta</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
+      <c r="H11" t="n">
         <v>152.222222222222</v>
       </c>
-      <c r="K11" t="n">
+      <c r="I11" t="n">
         <v>1.11111111111111</v>
       </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -992,8 +897,6 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1001,26 +904,18 @@
           <t>FAR WAE W21-05CvMagenta</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="3" t="n">
         <v>44385</v>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Magenta</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
+      <c r="D12" t="n">
         <v>0.57</v>
       </c>
-      <c r="G12" t="n">
+      <c r="E12" t="n">
         <v>0.0254950975679639</v>
       </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -1035,8 +930,6 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1044,26 +937,18 @@
           <t>FAR WAE W21-05CvMagenta</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="3" t="n">
         <v>44397</v>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Magenta</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
+      <c r="D13" t="n">
         <v>0.615</v>
       </c>
-      <c r="G13" t="n">
+      <c r="E13" t="n">
         <v>0.016583123951777</v>
       </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -1078,8 +963,6 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1087,26 +970,18 @@
           <t>FAR WAE W21-05CvMagenta</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="3" t="n">
         <v>44403</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Magenta</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
+      <c r="D14" t="n">
         <v>0.65</v>
       </c>
-      <c r="G14" t="n">
+      <c r="E14" t="n">
         <v>0.00707106781186548</v>
       </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -1121,8 +996,6 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1130,26 +1003,18 @@
           <t>FAR WAE W21-05CvMagenta</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="3" t="n">
         <v>44484</v>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Magenta</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
+      <c r="D15" t="n">
         <v>0.2675</v>
       </c>
-      <c r="G15" t="n">
+      <c r="E15" t="n">
         <v>0.0137689263682153</v>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -1164,8 +1029,6 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1173,26 +1036,18 @@
           <t>FAR WAE W21-05CvMagenta</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="3" t="n">
         <v>44498</v>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Magenta</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
+      <c r="D16" t="n">
         <v>0.165</v>
       </c>
-      <c r="G16" t="n">
+      <c r="E16" t="n">
         <v>0.00866025403784438</v>
       </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -1207,8 +1062,6 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1216,26 +1069,18 @@
           <t>FAR WAE W21-05CvMagenta</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="3" t="n">
         <v>44502</v>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Magenta</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
+      <c r="D17" t="n">
         <v>0.145</v>
       </c>
-      <c r="G17" t="n">
+      <c r="E17" t="n">
         <v>0.00288675134594812</v>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -1250,8 +1095,6 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1259,7 +1102,7 @@
           <t>FAR WAE W21-05CvMagenta</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -1267,32 +1110,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Magenta</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="n">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
         <v>1146.53832770366</v>
       </c>
-      <c r="I18" t="n">
+      <c r="G18" t="n">
         <v>0.225113709864247</v>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="n">
         <v>380.207589413489</v>
       </c>
-      <c r="M18" t="n">
+      <c r="K18" t="n">
         <v>16.9801087772997</v>
       </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -1301,8 +1136,6 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1310,7 +1143,7 @@
           <t>FAR WAE W21-05CvMagenta</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="3" t="n">
         <v>44538</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -1318,52 +1151,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Magenta</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>76.377</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.189417528227984</v>
+      </c>
       <c r="N19" t="n">
-        <v>76.377</v>
+        <v>9.85</v>
       </c>
       <c r="O19" t="n">
-        <v>0.189417528227984</v>
+        <v>0.0499999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>9.85</v>
+        <v>11.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0499999999999999</v>
+        <v>0.0645497224367905</v>
       </c>
       <c r="R19" t="n">
-        <v>11.35</v>
+        <v>2.12989603245515</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0645497224367905</v>
+        <v>0.139554648313736</v>
       </c>
       <c r="T19" t="n">
-        <v>2.12989603245515</v>
+        <v>561.132107699685</v>
       </c>
       <c r="U19" t="n">
-        <v>0.139554648313736</v>
-      </c>
-      <c r="V19" t="n">
-        <v>561.132107699685</v>
-      </c>
-      <c r="W19" t="n">
         <v>0.197158069963939</v>
       </c>
     </row>
@@ -1373,30 +1196,22 @@
           <t>FAR WAE W21-05CvCatapult</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="3" t="n">
         <v>44326</v>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Catapult</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
+      <c r="H20" t="n">
         <v>134.444444444444</v>
       </c>
-      <c r="K20" t="n">
+      <c r="I20" t="n">
         <v>5.55555555555555</v>
       </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -1407,8 +1222,6 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1416,26 +1229,18 @@
           <t>FAR WAE W21-05CvCatapult</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="3" t="n">
         <v>44385</v>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Catapult</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
+      <c r="D21" t="n">
         <v>0.635</v>
       </c>
-      <c r="G21" t="n">
+      <c r="E21" t="n">
         <v>0.0253311402559511</v>
       </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
@@ -1450,8 +1255,6 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1459,26 +1262,18 @@
           <t>FAR WAE W21-05CvCatapult</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="3" t="n">
         <v>44397</v>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Catapult</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
+      <c r="D22" t="n">
         <v>0.6925</v>
       </c>
-      <c r="G22" t="n">
+      <c r="E22" t="n">
         <v>0.00946484724300045</v>
       </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -1493,8 +1288,6 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1502,26 +1295,18 @@
           <t>FAR WAE W21-05CvCatapult</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="3" t="n">
         <v>44403</v>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Catapult</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
+      <c r="D23" t="n">
         <v>0.7025</v>
       </c>
-      <c r="G23" t="n">
+      <c r="E23" t="n">
         <v>0.0110867789130417</v>
       </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
@@ -1536,8 +1321,6 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1545,26 +1328,18 @@
           <t>FAR WAE W21-05CvCatapult</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="3" t="n">
         <v>44484</v>
       </c>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Catapult</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
+      <c r="D24" t="n">
         <v>0.36</v>
       </c>
-      <c r="G24" t="n">
+      <c r="E24" t="n">
         <v>0.0261406452355969</v>
       </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -1579,8 +1354,6 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1588,26 +1361,18 @@
           <t>FAR WAE W21-05CvCatapult</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="3" t="n">
         <v>44498</v>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Catapult</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
+      <c r="D25" t="n">
         <v>0.1525</v>
       </c>
-      <c r="G25" t="n">
+      <c r="E25" t="n">
         <v>0.0110867789130417</v>
       </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
@@ -1622,8 +1387,6 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1631,26 +1394,18 @@
           <t>FAR WAE W21-05CvCatapult</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="3" t="n">
         <v>44502</v>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Catapult</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
+      <c r="D26" t="n">
         <v>0.1375</v>
       </c>
-      <c r="G26" t="n">
+      <c r="E26" t="n">
         <v>0.00853912563829967</v>
       </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
@@ -1665,8 +1420,6 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1674,7 +1427,7 @@
           <t>FAR WAE W21-05CvCatapult</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -1682,32 +1435,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Catapult</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="n">
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
         <v>1435.14234867658</v>
       </c>
-      <c r="I27" t="n">
+      <c r="G27" t="n">
         <v>0.226583441863724</v>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="n">
         <v>416.029401208562</v>
       </c>
-      <c r="M27" t="n">
+      <c r="K27" t="n">
         <v>13.6979226031171</v>
       </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
@@ -1716,8 +1461,6 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1725,7 +1468,7 @@
           <t>FAR WAE W21-05CvCatapult</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="3" t="n">
         <v>44538</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -1733,52 +1476,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Catapult</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>77.852</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.133698666161382</v>
+      </c>
       <c r="N28" t="n">
-        <v>77.852</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>0.133698666161382</v>
+        <v>0.0577350269189631</v>
       </c>
       <c r="P28" t="n">
-        <v>9.800000000000001</v>
+        <v>11.35</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.0577350269189631</v>
+        <v>0.259807621135332</v>
       </c>
       <c r="R28" t="n">
-        <v>11.35</v>
+        <v>1.16080116389231</v>
       </c>
       <c r="S28" t="n">
-        <v>0.259807621135332</v>
+        <v>0.126449943558421</v>
       </c>
       <c r="T28" t="n">
-        <v>1.16080116389231</v>
+        <v>642.962873255769</v>
       </c>
       <c r="U28" t="n">
-        <v>0.126449943558421</v>
-      </c>
-      <c r="V28" t="n">
-        <v>642.962873255769</v>
-      </c>
-      <c r="W28" t="n">
         <v>0.12391452223174</v>
       </c>
     </row>
@@ -1788,30 +1521,22 @@
           <t>FAR WAE W21-05CvBennett</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="3" t="n">
         <v>44326</v>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="n">
+      <c r="H29" t="n">
         <v>178.888888888889</v>
       </c>
-      <c r="K29" t="n">
+      <c r="I29" t="n">
         <v>16.6666666666667</v>
       </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -1822,8 +1547,6 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1831,26 +1554,18 @@
           <t>FAR WAE W21-05CvBennett</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="3" t="n">
         <v>44385</v>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
+      <c r="D30" t="n">
         <v>0.7</v>
       </c>
-      <c r="G30" t="n">
+      <c r="E30" t="n">
         <v>0.0147196014438797</v>
       </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
@@ -1865,8 +1580,6 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1874,26 +1587,18 @@
           <t>FAR WAE W21-05CvBennett</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="3" t="n">
         <v>44397</v>
       </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
+      <c r="D31" t="n">
         <v>0.755</v>
       </c>
-      <c r="G31" t="n">
+      <c r="E31" t="n">
         <v>0.00957427107756339</v>
       </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
@@ -1908,8 +1613,6 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1917,26 +1620,18 @@
           <t>FAR WAE W21-05CvBennett</t>
         </is>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="3" t="n">
         <v>44403</v>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
+      <c r="D32" t="n">
         <v>0.7725</v>
       </c>
-      <c r="G32" t="n">
+      <c r="E32" t="n">
         <v>0.0047871355387817</v>
       </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -1951,8 +1646,6 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1960,26 +1653,18 @@
           <t>FAR WAE W21-05CvBennett</t>
         </is>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="3" t="n">
         <v>44484</v>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
+      <c r="D33" t="n">
         <v>0.65</v>
       </c>
-      <c r="G33" t="n">
+      <c r="E33" t="n">
         <v>0.00912870929175278</v>
       </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
@@ -1994,8 +1679,6 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2003,26 +1686,18 @@
           <t>FAR WAE W21-05CvBennett</t>
         </is>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="3" t="n">
         <v>44498</v>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
+      <c r="D34" t="n">
         <v>0.4975</v>
       </c>
-      <c r="G34" t="n">
+      <c r="E34" t="n">
         <v>0.0137689263682153</v>
       </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
@@ -2037,8 +1712,6 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2046,26 +1719,18 @@
           <t>FAR WAE W21-05CvBennett</t>
         </is>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="3" t="n">
         <v>44502</v>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
+      <c r="D35" t="n">
         <v>0.4625</v>
       </c>
-      <c r="G35" t="n">
+      <c r="E35" t="n">
         <v>0.0131497781983829</v>
       </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
@@ -2080,8 +1745,6 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2089,7 +1752,7 @@
           <t>FAR WAE W21-05CvBennett</t>
         </is>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -2097,32 +1760,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="n">
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
         <v>1851.17927688578</v>
       </c>
-      <c r="I36" t="n">
+      <c r="G36" t="n">
         <v>0.8833467753536099</v>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="n">
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="n">
         <v>442.616759181274</v>
       </c>
-      <c r="M36" t="n">
+      <c r="K36" t="n">
         <v>3.4761339522603</v>
       </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
@@ -2131,8 +1786,6 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2140,7 +1793,7 @@
           <t>FAR WAE W21-05CvBennett</t>
         </is>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="3" t="n">
         <v>44538</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -2148,52 +1801,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>81.04300000000001</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.535388021283004</v>
+      </c>
       <c r="N37" t="n">
-        <v>81.04300000000001</v>
+        <v>11.625</v>
       </c>
       <c r="O37" t="n">
-        <v>0.535388021283004</v>
+        <v>0.14361406616345</v>
       </c>
       <c r="P37" t="n">
-        <v>11.625</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.14361406616345</v>
+        <v>0.210158670215308</v>
       </c>
       <c r="R37" t="n">
-        <v>9.050000000000001</v>
+        <v>1.62892436438923</v>
       </c>
       <c r="S37" t="n">
-        <v>0.210158670215308</v>
+        <v>0.196041437831642</v>
       </c>
       <c r="T37" t="n">
-        <v>1.62892436438923</v>
+        <v>580.963357528749</v>
       </c>
       <c r="U37" t="n">
-        <v>0.196041437831642</v>
-      </c>
-      <c r="V37" t="n">
-        <v>580.963357528749</v>
-      </c>
-      <c r="W37" t="n">
         <v>0.261277494927817</v>
       </c>
     </row>
@@ -2203,30 +1846,22 @@
           <t>FAR WAE W21-05CvValiant CL</t>
         </is>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="3" t="n">
         <v>44326</v>
       </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Valiant CL</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
+      <c r="H38" t="n">
         <v>173.333333333333</v>
       </c>
-      <c r="K38" t="n">
+      <c r="I38" t="n">
         <v>13.3333333333333</v>
       </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -2237,8 +1872,6 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2246,26 +1879,18 @@
           <t>FAR WAE W21-05CvValiant CL</t>
         </is>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="3" t="n">
         <v>44385</v>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Valiant CL</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
+      <c r="D39" t="n">
         <v>0.59</v>
       </c>
-      <c r="G39" t="n">
+      <c r="E39" t="n">
         <v>0.0177951304200522</v>
       </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
@@ -2280,8 +1905,6 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2289,26 +1912,18 @@
           <t>FAR WAE W21-05CvValiant CL</t>
         </is>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="3" t="n">
         <v>44397</v>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Valiant CL</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
+      <c r="D40" t="n">
         <v>0.655</v>
       </c>
-      <c r="G40" t="n">
+      <c r="E40" t="n">
         <v>0.0125830573921179</v>
       </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
@@ -2323,8 +1938,6 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2332,26 +1945,18 @@
           <t>FAR WAE W21-05CvValiant CL</t>
         </is>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="3" t="n">
         <v>44403</v>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Valiant CL</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
+      <c r="D41" t="n">
         <v>0.6875</v>
       </c>
-      <c r="G41" t="n">
+      <c r="E41" t="n">
         <v>0.0103077640640441</v>
       </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
@@ -2366,8 +1971,6 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2375,26 +1978,18 @@
           <t>FAR WAE W21-05CvValiant CL</t>
         </is>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="3" t="n">
         <v>44484</v>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Valiant CL</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
+      <c r="D42" t="n">
         <v>0.4575</v>
       </c>
-      <c r="G42" t="n">
+      <c r="E42" t="n">
         <v>0.0275</v>
       </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
@@ -2409,8 +2004,6 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2418,26 +2011,18 @@
           <t>FAR WAE W21-05CvValiant CL</t>
         </is>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="3" t="n">
         <v>44498</v>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Valiant CL</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
+      <c r="D43" t="n">
         <v>0.2425</v>
       </c>
-      <c r="G43" t="n">
+      <c r="E43" t="n">
         <v>0.0193110503770941</v>
       </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
@@ -2452,8 +2037,6 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2461,26 +2044,18 @@
           <t>FAR WAE W21-05CvValiant CL</t>
         </is>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="3" t="n">
         <v>44502</v>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Valiant CL</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
+      <c r="D44" t="n">
         <v>0.19</v>
       </c>
-      <c r="G44" t="n">
+      <c r="E44" t="n">
         <v>0.00912870929175277</v>
       </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
@@ -2495,8 +2070,6 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2504,7 +2077,7 @@
           <t>FAR WAE W21-05CvValiant CL</t>
         </is>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="C45" t="inlineStr">
@@ -2512,32 +2085,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Valiant CL</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="n">
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
         <v>1557.5424123901</v>
       </c>
-      <c r="I45" t="n">
+      <c r="G45" t="n">
         <v>1.1062907647997</v>
       </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="n">
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="n">
         <v>404.286578939574</v>
       </c>
-      <c r="M45" t="n">
+      <c r="K45" t="n">
         <v>32.2135926003374</v>
       </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
@@ -2546,8 +2111,6 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2555,7 +2118,7 @@
           <t>FAR WAE W21-05CvValiant CL</t>
         </is>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="3" t="n">
         <v>44538</v>
       </c>
       <c r="C46" t="inlineStr">
@@ -2563,52 +2126,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Valiant CL</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="L46" t="n">
+        <v>80.03100000000001</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.498623772664988</v>
+      </c>
       <c r="N46" t="n">
-        <v>80.03100000000001</v>
+        <v>10.35</v>
       </c>
       <c r="O46" t="n">
-        <v>0.498623772664988</v>
+        <v>0.119023807142381</v>
       </c>
       <c r="P46" t="n">
-        <v>10.35</v>
+        <v>10.725</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.119023807142381</v>
+        <v>0.432772072419959</v>
       </c>
       <c r="R46" t="n">
-        <v>10.725</v>
+        <v>0.61213094239451</v>
       </c>
       <c r="S46" t="n">
-        <v>0.432772072419959</v>
+        <v>0.0625625074511154</v>
       </c>
       <c r="T46" t="n">
-        <v>0.61213094239451</v>
+        <v>605.717393896629</v>
       </c>
       <c r="U46" t="n">
-        <v>0.0625625074511154</v>
-      </c>
-      <c r="V46" t="n">
-        <v>605.717393896629</v>
-      </c>
-      <c r="W46" t="n">
         <v>0.144548067103383</v>
       </c>
     </row>
@@ -2618,30 +2171,22 @@
           <t>FAR WAE W21-05CvRockstar</t>
         </is>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="3" t="n">
         <v>44326</v>
       </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Rockstar</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="n">
+      <c r="H47" t="n">
         <v>147.777777777778</v>
       </c>
-      <c r="K47" t="n">
+      <c r="I47" t="n">
         <v>21.1111111111111</v>
       </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
@@ -2652,8 +2197,6 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2661,26 +2204,18 @@
           <t>FAR WAE W21-05CvRockstar</t>
         </is>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="3" t="n">
         <v>44385</v>
       </c>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Rockstar</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
+      <c r="D48" t="n">
         <v>0.5725</v>
       </c>
-      <c r="G48" t="n">
+      <c r="E48" t="n">
         <v>0.0344903368109581</v>
       </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
@@ -2695,8 +2230,6 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2704,26 +2237,18 @@
           <t>FAR WAE W21-05CvRockstar</t>
         </is>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="3" t="n">
         <v>44397</v>
       </c>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Rockstar</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
+      <c r="D49" t="n">
         <v>0.65</v>
       </c>
-      <c r="G49" t="n">
+      <c r="E49" t="n">
         <v>0.0355902608401043</v>
       </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
@@ -2738,8 +2263,6 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2747,26 +2270,18 @@
           <t>FAR WAE W21-05CvRockstar</t>
         </is>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="3" t="n">
         <v>44403</v>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Rockstar</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
+      <c r="D50" t="n">
         <v>0.665</v>
       </c>
-      <c r="G50" t="n">
+      <c r="E50" t="n">
         <v>0.0239791576165636</v>
       </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
@@ -2781,8 +2296,6 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2790,26 +2303,18 @@
           <t>FAR WAE W21-05CvRockstar</t>
         </is>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="3" t="n">
         <v>44484</v>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Rockstar</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
+      <c r="D51" t="n">
         <v>0.375</v>
       </c>
-      <c r="G51" t="n">
+      <c r="E51" t="n">
         <v>0.015545631755148</v>
       </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
@@ -2824,8 +2329,6 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2833,26 +2336,18 @@
           <t>FAR WAE W21-05CvRockstar</t>
         </is>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="3" t="n">
         <v>44498</v>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Rockstar</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
+      <c r="D52" t="n">
         <v>0.15</v>
       </c>
-      <c r="G52" t="n">
+      <c r="E52" t="n">
         <v>0.0108012344973464</v>
       </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
@@ -2867,8 +2362,6 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2876,26 +2369,18 @@
           <t>FAR WAE W21-05CvRockstar</t>
         </is>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="3" t="n">
         <v>44502</v>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Rockstar</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
+      <c r="D53" t="n">
         <v>0.1325</v>
       </c>
-      <c r="G53" t="n">
+      <c r="E53" t="n">
         <v>0.0075</v>
       </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
@@ -2910,8 +2395,6 @@
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2919,7 +2402,7 @@
           <t>FAR WAE W21-05CvRockstar</t>
         </is>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="C54" t="inlineStr">
@@ -2927,32 +2410,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Rockstar</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="n">
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="n">
         <v>1531.0785731474</v>
       </c>
-      <c r="I54" t="n">
+      <c r="G54" t="n">
         <v>0.76158260279395</v>
       </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="n">
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="n">
         <v>398.643669916145</v>
       </c>
-      <c r="M54" t="n">
+      <c r="K54" t="n">
         <v>23.0653732082669</v>
       </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
@@ -2961,8 +2436,6 @@
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2970,7 +2443,7 @@
           <t>FAR WAE W21-05CvRockstar</t>
         </is>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="3" t="n">
         <v>44538</v>
       </c>
       <c r="C55" t="inlineStr">
@@ -2978,52 +2451,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Rockstar</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+      <c r="L55" t="n">
+        <v>78.58799999999999</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.528047346362048</v>
+      </c>
       <c r="N55" t="n">
-        <v>78.58799999999999</v>
+        <v>10.175</v>
       </c>
       <c r="O55" t="n">
-        <v>0.528047346362048</v>
+        <v>0.0478713553878171</v>
       </c>
       <c r="P55" t="n">
-        <v>10.175</v>
+        <v>10.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.0478713553878171</v>
+        <v>0.273861278752583</v>
       </c>
       <c r="R55" t="n">
-        <v>10.3</v>
+        <v>0.866927598465986</v>
       </c>
       <c r="S55" t="n">
-        <v>0.273861278752583</v>
+        <v>0.114833014466158</v>
       </c>
       <c r="T55" t="n">
-        <v>0.866927598465986</v>
+        <v>656.000191083616</v>
       </c>
       <c r="U55" t="n">
-        <v>0.114833014466158</v>
-      </c>
-      <c r="V55" t="n">
-        <v>656.000191083616</v>
-      </c>
-      <c r="W55" t="n">
         <v>0.314702223235079</v>
       </c>
     </row>
@@ -3033,30 +2496,22 @@
           <t>FAR WAE W21-05CvAnapurna</t>
         </is>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="3" t="n">
         <v>44326</v>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="n">
+      <c r="H56" t="n">
         <v>148.888888888889</v>
       </c>
-      <c r="K56" t="n">
+      <c r="I56" t="n">
         <v>6.66666666666666</v>
       </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
@@ -3067,8 +2522,6 @@
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3076,26 +2529,18 @@
           <t>FAR WAE W21-05CvAnapurna</t>
         </is>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="3" t="n">
         <v>44385</v>
       </c>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
+      <c r="D57" t="n">
         <v>0.7</v>
       </c>
-      <c r="G57" t="n">
+      <c r="E57" t="n">
         <v>0.0227303028283098</v>
       </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
@@ -3110,8 +2555,6 @@
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3119,26 +2562,18 @@
           <t>FAR WAE W21-05CvAnapurna</t>
         </is>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="3" t="n">
         <v>44397</v>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
+      <c r="D58" t="n">
         <v>0.74</v>
       </c>
-      <c r="G58" t="n">
+      <c r="E58" t="n">
         <v>0.0173205080756888</v>
       </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
@@ -3153,8 +2588,6 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3162,26 +2595,18 @@
           <t>FAR WAE W21-05CvAnapurna</t>
         </is>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="3" t="n">
         <v>44403</v>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
+      <c r="D59" t="n">
         <v>0.76</v>
       </c>
-      <c r="G59" t="n">
+      <c r="E59" t="n">
         <v>0.0108012344973464</v>
       </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
@@ -3196,8 +2621,6 @@
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3205,26 +2628,18 @@
           <t>FAR WAE W21-05CvAnapurna</t>
         </is>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="3" t="n">
         <v>44484</v>
       </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
+      <c r="D60" t="n">
         <v>0.6175</v>
       </c>
-      <c r="G60" t="n">
+      <c r="E60" t="n">
         <v>0.0125</v>
       </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
@@ -3239,8 +2654,6 @@
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3248,26 +2661,18 @@
           <t>FAR WAE W21-05CvAnapurna</t>
         </is>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="3" t="n">
         <v>44498</v>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
+      <c r="D61" t="n">
         <v>0.41</v>
       </c>
-      <c r="G61" t="n">
+      <c r="E61" t="n">
         <v>0.0541602560309064</v>
       </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
@@ -3282,8 +2687,6 @@
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3291,26 +2694,18 @@
           <t>FAR WAE W21-05CvAnapurna</t>
         </is>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="3" t="n">
         <v>44502</v>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
+      <c r="D62" t="n">
         <v>0.34</v>
       </c>
-      <c r="G62" t="n">
+      <c r="E62" t="n">
         <v>0.0669576980886689</v>
       </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
@@ -3325,8 +2720,6 @@
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3334,7 +2727,7 @@
           <t>FAR WAE W21-05CvAnapurna</t>
         </is>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="C63" t="inlineStr">
@@ -3342,32 +2735,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="n">
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="n">
         <v>1664.70177159267</v>
       </c>
-      <c r="I63" t="n">
+      <c r="G63" t="n">
         <v>0.218698139699738</v>
       </c>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="n">
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="n">
         <v>468.202614618096</v>
       </c>
-      <c r="M63" t="n">
+      <c r="K63" t="n">
         <v>21.6562834068971</v>
       </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
@@ -3376,8 +2761,6 @@
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3385,7 +2768,7 @@
           <t>FAR WAE W21-05CvAnapurna</t>
         </is>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="3" t="n">
         <v>44538</v>
       </c>
       <c r="C64" t="inlineStr">
@@ -3393,52 +2776,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+      <c r="L64" t="n">
+        <v>78.3095</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.501297233851001</v>
+      </c>
       <c r="N64" t="n">
-        <v>78.3095</v>
+        <v>10.9</v>
       </c>
       <c r="O64" t="n">
-        <v>0.501297233851001</v>
+        <v>0.227303028283097</v>
       </c>
       <c r="P64" t="n">
-        <v>10.9</v>
+        <v>10.65</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.227303028283097</v>
+        <v>0.551513070259143</v>
       </c>
       <c r="R64" t="n">
-        <v>10.65</v>
+        <v>1.51131680481834</v>
       </c>
       <c r="S64" t="n">
-        <v>0.551513070259143</v>
+        <v>0.395427913450182</v>
       </c>
       <c r="T64" t="n">
-        <v>1.51131680481834</v>
+        <v>548.75576487234</v>
       </c>
       <c r="U64" t="n">
-        <v>0.395427913450182</v>
-      </c>
-      <c r="V64" t="n">
-        <v>548.75576487234</v>
-      </c>
-      <c r="W64" t="n">
         <v>0.213631403419483</v>
       </c>
     </row>
@@ -3448,30 +2821,22 @@
           <t>FAR WAE W21-05CvScepter</t>
         </is>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="3" t="n">
         <v>44326</v>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="n">
+      <c r="H65" t="n">
         <v>154.444444444444</v>
       </c>
-      <c r="K65" t="n">
+      <c r="I65" t="n">
         <v>14.4444444444444</v>
       </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
@@ -3482,8 +2847,6 @@
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3491,26 +2854,18 @@
           <t>FAR WAE W21-05CvScepter</t>
         </is>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="3" t="n">
         <v>44385</v>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
+      <c r="D66" t="n">
         <v>0.6075</v>
       </c>
-      <c r="G66" t="n">
+      <c r="E66" t="n">
         <v>0.0143614066163451</v>
       </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
@@ -3525,8 +2880,6 @@
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3534,26 +2887,18 @@
           <t>FAR WAE W21-05CvScepter</t>
         </is>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="3" t="n">
         <v>44397</v>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
+      <c r="D67" t="n">
         <v>0.645</v>
       </c>
-      <c r="G67" t="n">
+      <c r="E67" t="n">
         <v>0.0253311402559511</v>
       </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
@@ -3568,8 +2913,6 @@
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3577,26 +2920,18 @@
           <t>FAR WAE W21-05CvScepter</t>
         </is>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="3" t="n">
         <v>44403</v>
       </c>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
+      <c r="D68" t="n">
         <v>0.6775</v>
       </c>
-      <c r="G68" t="n">
+      <c r="E68" t="n">
         <v>0.0143614066163451</v>
       </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
@@ -3611,8 +2946,6 @@
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3620,26 +2953,18 @@
           <t>FAR WAE W21-05CvScepter</t>
         </is>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="3" t="n">
         <v>44484</v>
       </c>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
+      <c r="D69" t="n">
         <v>0.2675</v>
       </c>
-      <c r="G69" t="n">
+      <c r="E69" t="n">
         <v>0.025617376914899</v>
       </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
@@ -3654,8 +2979,6 @@
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3663,26 +2986,18 @@
           <t>FAR WAE W21-05CvScepter</t>
         </is>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="3" t="n">
         <v>44498</v>
       </c>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
+      <c r="D70" t="n">
         <v>0.1675</v>
       </c>
-      <c r="G70" t="n">
+      <c r="E70" t="n">
         <v>0.0110867789130417</v>
       </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
@@ -3697,8 +3012,6 @@
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3706,26 +3019,18 @@
           <t>FAR WAE W21-05CvScepter</t>
         </is>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="3" t="n">
         <v>44502</v>
       </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
+      <c r="D71" t="n">
         <v>0.1425</v>
       </c>
-      <c r="G71" t="n">
+      <c r="E71" t="n">
         <v>0.00629152869605896</v>
       </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
@@ -3740,8 +3045,6 @@
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3749,7 +3052,7 @@
           <t>FAR WAE W21-05CvScepter</t>
         </is>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="C72" t="inlineStr">
@@ -3757,32 +3060,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="n">
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="n">
         <v>1257.94930436656</v>
       </c>
-      <c r="I72" t="n">
+      <c r="G72" t="n">
         <v>0.757457174121405</v>
       </c>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="n">
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="n">
         <v>370.593393083687</v>
       </c>
-      <c r="M72" t="n">
+      <c r="K72" t="n">
         <v>25.6585982179376</v>
       </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
@@ -3791,8 +3086,6 @@
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3800,7 +3093,7 @@
           <t>FAR WAE W21-05CvScepter</t>
         </is>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="3" t="n">
         <v>44538</v>
       </c>
       <c r="C73" t="inlineStr">
@@ -3808,52 +3101,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Scepter</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
+      <c r="L73" t="n">
+        <v>78.408</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.179879589355399</v>
+      </c>
       <c r="N73" t="n">
-        <v>78.408</v>
+        <v>10</v>
       </c>
       <c r="O73" t="n">
-        <v>0.179879589355399</v>
+        <v>0.0577350269189624</v>
       </c>
       <c r="P73" t="n">
-        <v>10</v>
+        <v>11.95</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.0577350269189624</v>
+        <v>0.15545631755148</v>
       </c>
       <c r="R73" t="n">
-        <v>11.95</v>
+        <v>0.711193780806979</v>
       </c>
       <c r="S73" t="n">
-        <v>0.15545631755148</v>
+        <v>0.0268392296694101</v>
       </c>
       <c r="T73" t="n">
-        <v>0.711193780806979</v>
+        <v>587.241399505152</v>
       </c>
       <c r="U73" t="n">
-        <v>0.0268392296694101</v>
-      </c>
-      <c r="V73" t="n">
-        <v>587.241399505152</v>
-      </c>
-      <c r="W73" t="n">
         <v>0.07242046973014581</v>
       </c>
     </row>
@@ -3863,30 +3146,22 @@
           <t>FAR WAE W21-05CvIllabo</t>
         </is>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="3" t="n">
         <v>44326</v>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="n">
+      <c r="H74" t="n">
         <v>157.777777777778</v>
       </c>
-      <c r="K74" t="n">
+      <c r="I74" t="n">
         <v>15.5555555555556</v>
       </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
@@ -3897,8 +3172,6 @@
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3906,26 +3179,18 @@
           <t>FAR WAE W21-05CvIllabo</t>
         </is>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="3" t="n">
         <v>44385</v>
       </c>
       <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
+      <c r="D75" t="n">
         <v>0.715</v>
       </c>
-      <c r="G75" t="n">
+      <c r="E75" t="n">
         <v>0.0232737334062815</v>
       </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
@@ -3940,8 +3205,6 @@
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3949,26 +3212,18 @@
           <t>FAR WAE W21-05CvIllabo</t>
         </is>
       </c>
-      <c r="B76" s="1" t="n">
+      <c r="B76" s="3" t="n">
         <v>44397</v>
       </c>
       <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
+      <c r="D76" t="n">
         <v>0.75</v>
       </c>
-      <c r="G76" t="n">
+      <c r="E76" t="n">
         <v>0.0163299316185545</v>
       </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
@@ -3983,8 +3238,6 @@
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3992,26 +3245,18 @@
           <t>FAR WAE W21-05CvIllabo</t>
         </is>
       </c>
-      <c r="B77" s="1" t="n">
+      <c r="B77" s="3" t="n">
         <v>44403</v>
       </c>
       <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
+      <c r="D77" t="n">
         <v>0.7675</v>
       </c>
-      <c r="G77" t="n">
+      <c r="E77" t="n">
         <v>0.00629152869605898</v>
       </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
@@ -4026,8 +3271,6 @@
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4035,26 +3278,18 @@
           <t>FAR WAE W21-05CvIllabo</t>
         </is>
       </c>
-      <c r="B78" s="1" t="n">
+      <c r="B78" s="3" t="n">
         <v>44484</v>
       </c>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
+      <c r="D78" t="n">
         <v>0.57</v>
       </c>
-      <c r="G78" t="n">
+      <c r="E78" t="n">
         <v>0.0261406452355969</v>
       </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
@@ -4069,8 +3304,6 @@
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4078,26 +3311,18 @@
           <t>FAR WAE W21-05CvIllabo</t>
         </is>
       </c>
-      <c r="B79" s="1" t="n">
+      <c r="B79" s="3" t="n">
         <v>44498</v>
       </c>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
+      <c r="D79" t="n">
         <v>0.2875</v>
       </c>
-      <c r="G79" t="n">
+      <c r="E79" t="n">
         <v>0.0259406373604556</v>
       </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
@@ -4112,8 +3337,6 @@
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4121,26 +3344,18 @@
           <t>FAR WAE W21-05CvIllabo</t>
         </is>
       </c>
-      <c r="B80" s="1" t="n">
+      <c r="B80" s="3" t="n">
         <v>44502</v>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
+      <c r="D80" t="n">
         <v>0.225</v>
       </c>
-      <c r="G80" t="n">
+      <c r="E80" t="n">
         <v>0.0206155281280883</v>
       </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
@@ -4155,8 +3370,6 @@
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4164,7 +3377,7 @@
           <t>FAR WAE W21-05CvIllabo</t>
         </is>
       </c>
-      <c r="B81" s="1" t="n">
+      <c r="B81" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="C81" t="inlineStr">
@@ -4172,32 +3385,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="n">
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="n">
         <v>1652.34517070577</v>
       </c>
-      <c r="I81" t="n">
+      <c r="G81" t="n">
         <v>1.55530119732925</v>
       </c>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="n">
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="n">
         <v>451.867324126814</v>
       </c>
-      <c r="M81" t="n">
+      <c r="K81" t="n">
         <v>30.1817210963452</v>
       </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
@@ -4206,8 +3411,6 @@
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4215,7 +3418,7 @@
           <t>FAR WAE W21-05CvIllabo</t>
         </is>
       </c>
-      <c r="B82" s="1" t="n">
+      <c r="B82" s="3" t="n">
         <v>44538</v>
       </c>
       <c r="C82" t="inlineStr">
@@ -4223,52 +3426,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Illabo</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
+      <c r="L82" t="n">
+        <v>77.4545</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.863607694500228</v>
+      </c>
       <c r="N82" t="n">
-        <v>77.4545</v>
+        <v>10.375</v>
       </c>
       <c r="O82" t="n">
-        <v>0.863607694500228</v>
+        <v>0.06291528696058971</v>
       </c>
       <c r="P82" t="n">
-        <v>10.375</v>
+        <v>11.05</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.06291528696058971</v>
+        <v>0.272335577306136</v>
       </c>
       <c r="R82" t="n">
-        <v>11.05</v>
+        <v>0.463465912856754</v>
       </c>
       <c r="S82" t="n">
-        <v>0.272335577306136</v>
+        <v>0.0578023283930924</v>
       </c>
       <c r="T82" t="n">
-        <v>0.463465912856754</v>
+        <v>652.254357818657</v>
       </c>
       <c r="U82" t="n">
-        <v>0.0578023283930924</v>
-      </c>
-      <c r="V82" t="n">
-        <v>652.254357818657</v>
-      </c>
-      <c r="W82" t="n">
         <v>0.09492710962139859</v>
       </c>
     </row>
@@ -4278,30 +3471,22 @@
           <t>FAR WAE W21-05CvDenison</t>
         </is>
       </c>
-      <c r="B83" s="1" t="n">
+      <c r="B83" s="3" t="n">
         <v>44326</v>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Denison</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="n">
+      <c r="H83" t="n">
         <v>185.555555555556</v>
       </c>
-      <c r="K83" t="n">
+      <c r="I83" t="n">
         <v>1.11111111111111</v>
       </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
@@ -4312,8 +3497,6 @@
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4321,26 +3504,18 @@
           <t>FAR WAE W21-05CvDenison</t>
         </is>
       </c>
-      <c r="B84" s="1" t="n">
+      <c r="B84" s="3" t="n">
         <v>44385</v>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Denison</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
+      <c r="D84" t="n">
         <v>0.64</v>
       </c>
-      <c r="G84" t="n">
+      <c r="E84" t="n">
         <v>0.0234520787991171</v>
       </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
@@ -4355,8 +3530,6 @@
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4364,26 +3537,18 @@
           <t>FAR WAE W21-05CvDenison</t>
         </is>
       </c>
-      <c r="B85" s="1" t="n">
+      <c r="B85" s="3" t="n">
         <v>44397</v>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Denison</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
+      <c r="D85" t="n">
         <v>0.6875</v>
       </c>
-      <c r="G85" t="n">
+      <c r="E85" t="n">
         <v>0.0143614066163451</v>
       </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
@@ -4398,8 +3563,6 @@
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4407,26 +3570,18 @@
           <t>FAR WAE W21-05CvDenison</t>
         </is>
       </c>
-      <c r="B86" s="1" t="n">
+      <c r="B86" s="3" t="n">
         <v>44403</v>
       </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Denison</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
+      <c r="D86" t="n">
         <v>0.695</v>
       </c>
-      <c r="G86" t="n">
+      <c r="E86" t="n">
         <v>0.0125830573921179</v>
       </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
@@ -4441,8 +3596,6 @@
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4450,26 +3603,18 @@
           <t>FAR WAE W21-05CvDenison</t>
         </is>
       </c>
-      <c r="B87" s="1" t="n">
+      <c r="B87" s="3" t="n">
         <v>44484</v>
       </c>
       <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Denison</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
+      <c r="D87" t="n">
         <v>0.4375</v>
       </c>
-      <c r="G87" t="n">
+      <c r="E87" t="n">
         <v>0.0143614066163451</v>
       </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
@@ -4484,8 +3629,6 @@
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4493,26 +3636,18 @@
           <t>FAR WAE W21-05CvDenison</t>
         </is>
       </c>
-      <c r="B88" s="1" t="n">
+      <c r="B88" s="3" t="n">
         <v>44498</v>
       </c>
       <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Denison</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
+      <c r="D88" t="n">
         <v>0.1925</v>
       </c>
-      <c r="G88" t="n">
+      <c r="E88" t="n">
         <v>0.00853912563829967</v>
       </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
@@ -4527,8 +3662,6 @@
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4536,26 +3669,18 @@
           <t>FAR WAE W21-05CvDenison</t>
         </is>
       </c>
-      <c r="B89" s="1" t="n">
+      <c r="B89" s="3" t="n">
         <v>44502</v>
       </c>
       <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Denison</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
+      <c r="D89" t="n">
         <v>0.1575</v>
       </c>
-      <c r="G89" t="n">
+      <c r="E89" t="n">
         <v>0.0047871355387817</v>
       </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
@@ -4570,8 +3695,6 @@
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4579,7 +3702,7 @@
           <t>FAR WAE W21-05CvDenison</t>
         </is>
       </c>
-      <c r="B90" s="1" t="n">
+      <c r="B90" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="C90" t="inlineStr">
@@ -4587,32 +3710,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Denison</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="n">
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="n">
         <v>1488.0129550422</v>
       </c>
-      <c r="I90" t="n">
+      <c r="G90" t="n">
         <v>0.23403436888351</v>
       </c>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="n">
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="n">
         <v>398.753103446794</v>
       </c>
-      <c r="M90" t="n">
+      <c r="K90" t="n">
         <v>21.4830632290292</v>
       </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
@@ -4621,8 +3736,6 @@
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4630,7 +3743,7 @@
           <t>FAR WAE W21-05CvDenison</t>
         </is>
       </c>
-      <c r="B91" s="1" t="n">
+      <c r="B91" s="3" t="n">
         <v>44538</v>
       </c>
       <c r="C91" t="inlineStr">
@@ -4638,52 +3751,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Denison</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
+      <c r="L91" t="n">
+        <v>77.45699999999999</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.255292642536624</v>
+      </c>
       <c r="N91" t="n">
-        <v>77.45699999999999</v>
+        <v>9.75</v>
       </c>
       <c r="O91" t="n">
-        <v>0.255292642536624</v>
+        <v>0.08660254037844391</v>
       </c>
       <c r="P91" t="n">
-        <v>9.75</v>
+        <v>11.2</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.08660254037844391</v>
+        <v>0.324037034920393</v>
       </c>
       <c r="R91" t="n">
-        <v>11.2</v>
+        <v>1.38258254123884</v>
       </c>
       <c r="S91" t="n">
-        <v>0.324037034920393</v>
+        <v>0.101601669330571</v>
       </c>
       <c r="T91" t="n">
-        <v>1.38258254123884</v>
+        <v>671.1020331807219</v>
       </c>
       <c r="U91" t="n">
-        <v>0.101601669330571</v>
-      </c>
-      <c r="V91" t="n">
-        <v>671.1020331807219</v>
-      </c>
-      <c r="W91" t="n">
         <v>0.08443221418559339</v>
       </c>
     </row>
